--- a/data/config/aplicacoes_fundos.xlsx
+++ b/data/config/aplicacoes_fundos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Windows 11\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{72191B5C-B308-47D9-9DC9-0588D813421F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81AED69E-649E-4507-A59E-96DD067560F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{7416F21D-5932-4029-913F-23D06D3BD085}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="7">
   <si>
     <t xml:space="preserve">Conta </t>
   </si>
@@ -420,7 +420,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAA1C7B1-216A-4C6A-B3D2-C0F16635EE8F}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="37.5703125" bestFit="1" customWidth="1"/>
@@ -484,6 +484,34 @@
         <v>1000000</v>
       </c>
     </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>7983962</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="1">
+        <v>46197</v>
+      </c>
+      <c r="D5" s="2">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>7983962</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="1">
+        <v>46197</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1000000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/data/config/aplicacoes_fundos.xlsx
+++ b/data/config/aplicacoes_fundos.xlsx
@@ -1,40 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Windows 11\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Computador\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81AED69E-649E-4507-A59E-96DD067560F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B32811FB-699A-45D3-8BE3-15DB736BCC3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{7416F21D-5932-4029-913F-23D06D3BD085}"/>
+    <workbookView xWindow="28740" yWindow="-16320" windowWidth="29040" windowHeight="15840" xr2:uid="{7416F21D-5932-4029-913F-23D06D3BD085}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="9">
   <si>
     <t xml:space="preserve">Conta </t>
   </si>
@@ -45,9 +36,6 @@
     <t xml:space="preserve">Data de Aplicação </t>
   </si>
   <si>
-    <t xml:space="preserve">Valor Aplicação </t>
-  </si>
-  <si>
     <t>Bradesco Bancos II FIF CIC RF CP RL</t>
   </si>
   <si>
@@ -55,6 +43,15 @@
   </si>
   <si>
     <t>Safra Extra Bancos Special FIC FIRF CP</t>
+  </si>
+  <si>
+    <t>Tipo</t>
+  </si>
+  <si>
+    <t>Valor</t>
+  </si>
+  <si>
+    <t>Aplicação</t>
   </si>
 </sst>
 </file>
@@ -420,15 +417,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAA1C7B1-216A-4C6A-B3D2-C0F16635EE8F}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="37.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.28515625" customWidth="1"/>
+    <col min="5" max="5" width="15.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -439,76 +437,94 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="E1" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>7983962</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" s="1">
         <v>46155</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="2">
         <v>500000</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>7983962</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3" s="1">
         <v>46154</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="2">
         <v>500000</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>7983962</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" s="1">
         <v>46154</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="2">
         <v>1000000</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>7983962</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C5" s="1">
         <v>46197</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="2">
         <v>1000000</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>7983962</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" s="1">
         <v>46197</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="2">
         <v>1000000</v>
       </c>
     </row>

--- a/data/config/aplicacoes_fundos.xlsx
+++ b/data/config/aplicacoes_fundos.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Computador\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Computador\Downloads\Aplicativos e Programação\Tesouraria\App Tesouraria Botuverá\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B32811FB-699A-45D3-8BE3-15DB736BCC3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DF3B9EE-5254-401C-913C-A458B9D91FB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28740" yWindow="-16320" windowWidth="29040" windowHeight="15840" xr2:uid="{7416F21D-5932-4029-913F-23D06D3BD085}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="14">
   <si>
     <t xml:space="preserve">Conta </t>
   </si>
@@ -33,9 +33,6 @@
     <t xml:space="preserve">Fundo </t>
   </si>
   <si>
-    <t xml:space="preserve">Data de Aplicação </t>
-  </si>
-  <si>
     <t>Bradesco Bancos II FIF CIC RF CP RL</t>
   </si>
   <si>
@@ -52,6 +49,24 @@
   </si>
   <si>
     <t>Aplicação</t>
+  </si>
+  <si>
+    <t>Safra Vitesse Classe de Investimento RF CP RL</t>
+  </si>
+  <si>
+    <t>Data</t>
+  </si>
+  <si>
+    <t>Resgate</t>
+  </si>
+  <si>
+    <t>XP Bancos FIRF Referenciada DI CP RL</t>
+  </si>
+  <si>
+    <t>Safra DI Master FIRF Referenciado DI LP</t>
+  </si>
+  <si>
+    <t>Bradesco Zupo FIF CIC RF CP LP RL</t>
   </si>
 </sst>
 </file>
@@ -417,13 +432,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAA1C7B1-216A-4C6A-B3D2-C0F16635EE8F}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="37.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.28515625" customWidth="1"/>
-    <col min="5" max="5" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -434,13 +449,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" t="s">
         <v>6</v>
-      </c>
-      <c r="E1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -448,13 +463,13 @@
         <v>7983962</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1">
-        <v>46155</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>8</v>
+        <v>46154</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
       </c>
       <c r="E2" s="2">
         <v>500000</v>
@@ -465,13 +480,13 @@
         <v>7983962</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3" s="1">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E3" s="2">
         <v>500000</v>
@@ -482,16 +497,16 @@
         <v>7983962</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C4" s="1">
         <v>46154</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E4" s="2">
-        <v>1000000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -502,10 +517,10 @@
         <v>4</v>
       </c>
       <c r="C5" s="1">
-        <v>46197</v>
+        <v>46154</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E5" s="2">
         <v>1000000</v>
@@ -516,16 +531,220 @@
         <v>7983962</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C6" s="1">
         <v>46197</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E6" s="2">
         <v>1000000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>7983962</v>
+      </c>
+      <c r="B7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="1">
+        <v>46197</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7983962</v>
+      </c>
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="1">
+        <v>46157</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="2">
+        <v>506266.45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>7983962</v>
+      </c>
+      <c r="B9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="1">
+        <v>46216</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="2">
+        <v>100500</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>7983962</v>
+      </c>
+      <c r="B10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="1">
+        <v>46223</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="2">
+        <v>690000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>7983962</v>
+      </c>
+      <c r="B11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11" s="1">
+        <v>46233</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="2">
+        <v>1507000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>4163084</v>
+      </c>
+      <c r="B12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="1">
+        <v>46252</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="2">
+        <v>4000000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>4163084</v>
+      </c>
+      <c r="B13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="1">
+        <v>46252</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="2">
+        <v>2000000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>4163084</v>
+      </c>
+      <c r="B14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="1">
+        <v>46252</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="2">
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>4163084</v>
+      </c>
+      <c r="B15" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="1">
+        <v>46252</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" s="2">
+        <v>2000000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>4163084</v>
+      </c>
+      <c r="B16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="1">
+        <v>46252</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16" s="2">
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>4163084</v>
+      </c>
+      <c r="B17" t="s">
+        <v>3</v>
+      </c>
+      <c r="C17" s="1">
+        <v>46252</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" s="2">
+        <v>2000000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>4163084</v>
+      </c>
+      <c r="B18" t="s">
+        <v>2</v>
+      </c>
+      <c r="C18" s="1">
+        <v>46252</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18" s="2">
+        <v>2000000</v>
       </c>
     </row>
   </sheetData>

--- a/data/config/aplicacoes_fundos.xlsx
+++ b/data/config/aplicacoes_fundos.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Computador\Downloads\Aplicativos e Programação\Tesouraria\App Tesouraria Botuverá\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Computador\Downloads\Aplicativos e Programação\Tesouraria\App Tesouraria Botuverá\Código\data\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DF3B9EE-5254-401C-913C-A458B9D91FB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA3EC2EB-6233-4C8F-8217-298F1EF6B1D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28740" yWindow="-16320" windowWidth="29040" windowHeight="15840" xr2:uid="{7416F21D-5932-4029-913F-23D06D3BD085}"/>
+    <workbookView xWindow="-60" yWindow="-16425" windowWidth="29040" windowHeight="15840" xr2:uid="{7416F21D-5932-4029-913F-23D06D3BD085}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="14">
   <si>
     <t xml:space="preserve">Conta </t>
   </si>
@@ -432,7 +432,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAA1C7B1-216A-4C6A-B3D2-C0F16635EE8F}">
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="42.28515625" bestFit="1" customWidth="1"/>
@@ -747,6 +747,142 @@
         <v>2000000</v>
       </c>
     </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>11370136</v>
+      </c>
+      <c r="B19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="1">
+        <v>46253</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" s="2">
+        <v>467000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>5166121</v>
+      </c>
+      <c r="B20" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="1">
+        <v>46253</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="2">
+        <v>2000000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>5166121</v>
+      </c>
+      <c r="B21" t="s">
+        <v>3</v>
+      </c>
+      <c r="C21" s="1">
+        <v>46253</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E21" s="2">
+        <v>2000000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>5166121</v>
+      </c>
+      <c r="B22" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="1">
+        <v>46253</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E22" s="2">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>4163084</v>
+      </c>
+      <c r="B23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="1">
+        <v>46254</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23" s="2">
+        <v>4004098.72</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>4163084</v>
+      </c>
+      <c r="B24" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="1">
+        <v>46254</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E24" s="2">
+        <v>2002084.9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>4163084</v>
+      </c>
+      <c r="B25" t="s">
+        <v>4</v>
+      </c>
+      <c r="C25" s="1">
+        <v>46254</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E25" s="2">
+        <v>1001000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>4163084</v>
+      </c>
+      <c r="B26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="1">
+        <v>46254</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E26" s="2">
+        <v>1500783.35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
